--- a/4_outputs/final/Table24.xlsx
+++ b/4_outputs/final/Table24.xlsx
@@ -423,10 +423,10 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1120,32 +1120,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.775</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.544</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.868</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.662</t>
         </is>
       </c>
     </row>

--- a/4_outputs/final/Table24.xlsx
+++ b/4_outputs/final/Table24.xlsx
@@ -417,737 +417,923 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Research (segments)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Policy (segments)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Semantic-gap rank</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SDG</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Policy source</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Retrieval</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Canon</t>
+          <t>n_LR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Curated</t>
+          <t>Agree %</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SDGi</t>
+          <t>Res MLP %</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNGDC</t>
+          <t>n_LR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Agree %</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MLP</t>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>||</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 (No Poverty)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>13,459</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>30.9</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1,700</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>6</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 (Zero Hunger)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>78,591</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1,723</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>3 (Good Health)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>859,355</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2,934</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 (Education)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>470,002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2,055</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 (Gender Equality)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>64,940</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 (Clean Water)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>35,137</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1,206</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 (Clean Energy)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>119,467</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1,808</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>8 (Decent Work)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>65,500</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2,016</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>9 (Innovation)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>577,833</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4,066</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10 (Reduced Ineq.)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>30,323</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1,123</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>9</t>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>11 (Sust. Cities)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>146,508</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1,658</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>12 (Consumption)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>46,199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1,187</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>13 (Climate)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>121,557</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>40.5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3,399</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>5</t>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 (Life Below Water)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>51,458</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1,634</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15 (Life on Land)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>78,102</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>70.3</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1,828</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16 (Peace &amp; Justice)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>337,317</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5,725</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>17 (Partnerships)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>9,396</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4,509</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>84.1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rank Corr (ρ)</t>
+          <t>Overall</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3,105,144</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>40,597</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.868</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.662</t>
-        </is>
-      </c>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
